--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U278"/>
+  <dimension ref="A1:U279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19634,6 +19634,75 @@
       <c r="U278" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>376.93</v>
+      </c>
+      <c r="C279" t="n">
+        <v>379.1</v>
+      </c>
+      <c r="D279" t="n">
+        <v>381.71</v>
+      </c>
+      <c r="E279" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="F279" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="G279" t="n">
+        <v>378.76</v>
+      </c>
+      <c r="H279" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="I279" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="J279" t="n">
+        <v>387.78</v>
+      </c>
+      <c r="K279" t="n">
+        <v>386.12</v>
+      </c>
+      <c r="L279" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="M279" t="n">
+        <v>358.21</v>
+      </c>
+      <c r="N279" t="n">
+        <v>353.62</v>
+      </c>
+      <c r="O279" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="P279" t="n">
+        <v>359.48</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="R279" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="S279" t="n">
+        <v>376.18</v>
+      </c>
+      <c r="T279" t="n">
+        <v>381.36</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19648,7 +19717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22511,6 +22580,16 @@
       </c>
       <c r="B286" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -22679,28 +22758,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009942357103580783</v>
+        <v>0.006079676020994171</v>
       </c>
       <c r="J2" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K2" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001178682632685391</v>
+        <v>4.434256893559585e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.894249122820702</v>
+        <v>4.895430310548369</v>
       </c>
       <c r="N2" t="n">
-        <v>39.7203536743065</v>
+        <v>39.66382243526386</v>
       </c>
       <c r="O2" t="n">
-        <v>6.302408561360212</v>
+        <v>6.297922072816069</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5999680959798</v>
+        <v>381.6437155611868</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22757,28 +22836,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01298007688021539</v>
+        <v>0.00898545082925902</v>
       </c>
       <c r="J3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002518371975377409</v>
+        <v>0.0001213359553129401</v>
       </c>
       <c r="M3" t="n">
-        <v>4.360666421618425</v>
+        <v>4.359738546883583</v>
       </c>
       <c r="N3" t="n">
-        <v>31.68164582909199</v>
+        <v>31.66003064695738</v>
       </c>
       <c r="O3" t="n">
-        <v>5.628645114864854</v>
+        <v>5.626724681993724</v>
       </c>
       <c r="P3" t="n">
-        <v>383.8541906496653</v>
+        <v>383.8994324805188</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22835,28 +22914,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01719213363599827</v>
+        <v>0.01437554705249001</v>
       </c>
       <c r="J4" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K4" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005471300767336817</v>
+        <v>0.0003850568281712485</v>
       </c>
       <c r="M4" t="n">
-        <v>3.712862399388736</v>
+        <v>3.71405929230691</v>
       </c>
       <c r="N4" t="n">
-        <v>25.57488884670736</v>
+        <v>25.52880412748043</v>
       </c>
       <c r="O4" t="n">
-        <v>5.057162133717621</v>
+        <v>5.052603697845343</v>
       </c>
       <c r="P4" t="n">
-        <v>384.8546981625335</v>
+        <v>384.8865979028771</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22913,28 +22992,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06855319248765504</v>
+        <v>0.06683374092312414</v>
       </c>
       <c r="J5" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K5" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007178226510975994</v>
+        <v>0.006877004075391047</v>
       </c>
       <c r="M5" t="n">
-        <v>4.11134166206338</v>
+        <v>4.106012692846998</v>
       </c>
       <c r="N5" t="n">
-        <v>30.78874394004883</v>
+        <v>30.69510318502788</v>
       </c>
       <c r="O5" t="n">
-        <v>5.548760576926061</v>
+        <v>5.540316162912355</v>
       </c>
       <c r="P5" t="n">
-        <v>380.7977692663682</v>
+        <v>380.8172432135789</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22991,28 +23070,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03184585279246864</v>
+        <v>-0.02878972116182376</v>
       </c>
       <c r="J6" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K6" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001449219959598125</v>
+        <v>0.001192505143304268</v>
       </c>
       <c r="M6" t="n">
-        <v>4.384400620461928</v>
+        <v>4.379758983767578</v>
       </c>
       <c r="N6" t="n">
-        <v>33.09970195512678</v>
+        <v>33.034690972043</v>
       </c>
       <c r="O6" t="n">
-        <v>5.753234043138414</v>
+        <v>5.747581314957015</v>
       </c>
       <c r="P6" t="n">
-        <v>377.9990989555088</v>
+        <v>377.964486206146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23069,28 +23148,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02220201263238213</v>
+        <v>0.02601048169436311</v>
       </c>
       <c r="J7" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K7" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004658216425831307</v>
+        <v>0.0006434003720077186</v>
       </c>
       <c r="M7" t="n">
-        <v>4.978971646195765</v>
+        <v>4.977900328798079</v>
       </c>
       <c r="N7" t="n">
-        <v>50.10085595704645</v>
+        <v>50.00457804103397</v>
       </c>
       <c r="O7" t="n">
-        <v>7.078195812284826</v>
+        <v>7.071391520841846</v>
       </c>
       <c r="P7" t="n">
-        <v>373.3186249389702</v>
+        <v>373.2754914614143</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23147,28 +23226,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1123175963691664</v>
+        <v>-0.1040604961910888</v>
       </c>
       <c r="J8" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K8" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00998591166433449</v>
+        <v>0.008596781281477894</v>
       </c>
       <c r="M8" t="n">
-        <v>6.017884772008318</v>
+        <v>6.029335863391175</v>
       </c>
       <c r="N8" t="n">
-        <v>59.24227459666005</v>
+        <v>59.42374676901168</v>
       </c>
       <c r="O8" t="n">
-        <v>7.696900323939505</v>
+        <v>7.708679962808916</v>
       </c>
       <c r="P8" t="n">
-        <v>374.4867761906075</v>
+        <v>374.3932589690124</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23225,28 +23304,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1739691026889781</v>
+        <v>-0.1666199415327354</v>
       </c>
       <c r="J9" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K9" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03147581350001483</v>
+        <v>0.02897901852344831</v>
       </c>
       <c r="M9" t="n">
-        <v>5.278040461691603</v>
+        <v>5.295805954539037</v>
       </c>
       <c r="N9" t="n">
-        <v>44.112352820917</v>
+        <v>44.26624635346084</v>
       </c>
       <c r="O9" t="n">
-        <v>6.641713093842356</v>
+        <v>6.653288386464308</v>
       </c>
       <c r="P9" t="n">
-        <v>375.791347251882</v>
+        <v>375.7081130513075</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23303,28 +23382,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.145812057136369</v>
+        <v>-0.138602076519174</v>
       </c>
       <c r="J10" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K10" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02454751260969901</v>
+        <v>0.02224718705876705</v>
       </c>
       <c r="M10" t="n">
-        <v>5.09692988088299</v>
+        <v>5.109638226172335</v>
       </c>
       <c r="N10" t="n">
-        <v>40.01916023610566</v>
+        <v>40.17605046708449</v>
       </c>
       <c r="O10" t="n">
-        <v>6.326069888651695</v>
+        <v>6.338458051220698</v>
       </c>
       <c r="P10" t="n">
-        <v>382.414581263216</v>
+        <v>382.3329233759998</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23381,28 +23460,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08023183667957784</v>
+        <v>-0.07590657620094272</v>
       </c>
       <c r="J11" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K11" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003231773790027925</v>
+        <v>0.002914067166872369</v>
       </c>
       <c r="M11" t="n">
-        <v>7.796619119876471</v>
+        <v>7.792054526377931</v>
       </c>
       <c r="N11" t="n">
-        <v>94.04358317098423</v>
+        <v>93.81356431331363</v>
       </c>
       <c r="O11" t="n">
-        <v>9.697607084790775</v>
+        <v>9.685740256341465</v>
       </c>
       <c r="P11" t="n">
-        <v>382.7101240566765</v>
+        <v>382.6611375682104</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -23463,28 +23542,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05288699980556981</v>
+        <v>0.05134012661039722</v>
       </c>
       <c r="J12" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K12" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003351370874753457</v>
+        <v>0.003183683299864182</v>
       </c>
       <c r="M12" t="n">
-        <v>4.97066734322037</v>
+        <v>4.959642601107828</v>
       </c>
       <c r="N12" t="n">
-        <v>39.73798258220373</v>
+        <v>39.60686283656206</v>
       </c>
       <c r="O12" t="n">
-        <v>6.303806991192205</v>
+        <v>6.293398353557643</v>
       </c>
       <c r="P12" t="n">
-        <v>372.4754698174367</v>
+        <v>372.4929372952741</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -23545,28 +23624,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1383106199048184</v>
+        <v>-0.1384629398608674</v>
       </c>
       <c r="J13" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K13" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03278274815786653</v>
+        <v>0.03311336226225381</v>
       </c>
       <c r="M13" t="n">
-        <v>3.960420698531086</v>
+        <v>3.946697540700812</v>
       </c>
       <c r="N13" t="n">
-        <v>26.72005128110096</v>
+        <v>26.62302179608561</v>
       </c>
       <c r="O13" t="n">
-        <v>5.169144153639069</v>
+        <v>5.159750167991239</v>
       </c>
       <c r="P13" t="n">
-        <v>362.0414709572965</v>
+        <v>362.0432019741239</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23623,28 +23702,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1602102409913019</v>
+        <v>-0.1650776137627765</v>
       </c>
       <c r="J14" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K14" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02974224120684765</v>
+        <v>0.03166364148312761</v>
       </c>
       <c r="M14" t="n">
-        <v>4.984718023461312</v>
+        <v>4.991579054613956</v>
       </c>
       <c r="N14" t="n">
-        <v>39.66216788858691</v>
+        <v>39.65660610797983</v>
       </c>
       <c r="O14" t="n">
-        <v>6.297790714892558</v>
+        <v>6.29734913340366</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0397608318708</v>
+        <v>364.0948871072264</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23701,28 +23780,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1328298663903635</v>
+        <v>-0.1317930994348379</v>
       </c>
       <c r="J15" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K15" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02549026788392061</v>
+        <v>0.0253002295500695</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3771892363423</v>
+        <v>4.365174742277069</v>
       </c>
       <c r="N15" t="n">
-        <v>31.95109311358048</v>
+        <v>31.84238177039881</v>
       </c>
       <c r="O15" t="n">
-        <v>5.65252979767294</v>
+        <v>5.64290543695345</v>
       </c>
       <c r="P15" t="n">
-        <v>362.2812530483488</v>
+        <v>362.2695109641991</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23779,28 +23858,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08687187008030073</v>
+        <v>-0.08595337818258507</v>
       </c>
       <c r="J16" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K16" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01308198481320433</v>
+        <v>0.01291199808226795</v>
       </c>
       <c r="M16" t="n">
-        <v>4.050410396623361</v>
+        <v>4.039008575742403</v>
       </c>
       <c r="N16" t="n">
-        <v>26.96796932377926</v>
+        <v>26.87584453338445</v>
       </c>
       <c r="O16" t="n">
-        <v>5.193069354801577</v>
+        <v>5.184191791724574</v>
       </c>
       <c r="P16" t="n">
-        <v>360.5899446362911</v>
+        <v>360.5795420968428</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23857,28 +23936,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.07585248791768323</v>
+        <v>-0.07435559031187181</v>
       </c>
       <c r="J17" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K17" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01231061415767853</v>
+        <v>0.0119243595419013</v>
       </c>
       <c r="M17" t="n">
-        <v>3.36548205730849</v>
+        <v>3.358892335554435</v>
       </c>
       <c r="N17" t="n">
-        <v>21.86567028683742</v>
+        <v>21.79998433109894</v>
       </c>
       <c r="O17" t="n">
-        <v>4.676074238807317</v>
+        <v>4.669045334016253</v>
       </c>
       <c r="P17" t="n">
-        <v>363.6166108270688</v>
+        <v>363.5996574533553</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23935,28 +24014,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01338316025893982</v>
+        <v>0.01766090688346728</v>
       </c>
       <c r="J18" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K18" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0002210906683248748</v>
+        <v>0.0003870453327462497</v>
       </c>
       <c r="M18" t="n">
-        <v>4.327052814613216</v>
+        <v>4.328644213589252</v>
       </c>
       <c r="N18" t="n">
-        <v>38.3648393282969</v>
+        <v>38.33273810848957</v>
       </c>
       <c r="O18" t="n">
-        <v>6.193935689712713</v>
+        <v>6.191343804739773</v>
       </c>
       <c r="P18" t="n">
-        <v>366.4359443234075</v>
+        <v>366.387495961345</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24013,28 +24092,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0351781590325112</v>
+        <v>-0.0302601430135956</v>
       </c>
       <c r="J19" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K19" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001521687440986796</v>
+        <v>0.001131524343822354</v>
       </c>
       <c r="M19" t="n">
-        <v>4.560601834262502</v>
+        <v>4.564804144705732</v>
       </c>
       <c r="N19" t="n">
-        <v>38.4628856763438</v>
+        <v>38.46450581898991</v>
       </c>
       <c r="O19" t="n">
-        <v>6.20184534443933</v>
+        <v>6.201975960852308</v>
       </c>
       <c r="P19" t="n">
-        <v>370.8310881267396</v>
+        <v>370.7753882824928</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24091,28 +24170,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1167687101294208</v>
+        <v>-0.1126933871453226</v>
       </c>
       <c r="J20" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K20" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02672176918871239</v>
+        <v>0.02503458566080219</v>
       </c>
       <c r="M20" t="n">
-        <v>3.649561617219431</v>
+        <v>3.652697655255968</v>
       </c>
       <c r="N20" t="n">
-        <v>23.52378682917883</v>
+        <v>23.5352852458462</v>
       </c>
       <c r="O20" t="n">
-        <v>4.850132660987618</v>
+        <v>4.851317887527697</v>
       </c>
       <c r="P20" t="n">
-        <v>379.2336193453397</v>
+        <v>379.1874635673599</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24150,7 +24229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U278"/>
+  <dimension ref="A1:U279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53871,6 +53950,113 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>-35.673506659008574,174.5083048198493</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>-35.67423206655626,174.50840330815447</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-35.674950635051694,174.50850558060233</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-35.67566643445012,174.50863171611527</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>-35.676385291550666,174.50878322234814</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-35.6771087930944,174.50890389336504</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>-35.67782325728628,174.50908554094394</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-35.67854161631161,174.50921909750608</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-35.679194260476116,174.5094591409243</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-35.67976684212312,174.50995153234035</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-35.68048736536622,174.51013580353347</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>-35.68123204858679,174.50997979285086</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>-35.68196543980243,174.51005354782836</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-35.682673394428356,174.51028782904663</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-35.68339004135574,174.51045519186928</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>-35.68410346620155,174.51064401357976</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>-35.68480432270545,174.5108799692814</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>-35.68545986170714,174.51117988919893</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>-35.686059773297245,174.51166508100852</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U279"/>
+  <dimension ref="A1:U280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19701,6 +19701,75 @@
         <v>381.36</v>
       </c>
       <c r="U279" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>376.15</v>
+      </c>
+      <c r="C280" t="n">
+        <v>379.84</v>
+      </c>
+      <c r="D280" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="E280" t="n">
+        <v>380.49</v>
+      </c>
+      <c r="F280" t="n">
+        <v>383.87</v>
+      </c>
+      <c r="G280" t="n">
+        <v>379.01</v>
+      </c>
+      <c r="H280" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="I280" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="J280" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="K280" t="n">
+        <v>385.82</v>
+      </c>
+      <c r="L280" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="M280" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="N280" t="n">
+        <v>354.13</v>
+      </c>
+      <c r="O280" t="n">
+        <v>361.08</v>
+      </c>
+      <c r="P280" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>364.98</v>
+      </c>
+      <c r="R280" t="n">
+        <v>372.72</v>
+      </c>
+      <c r="S280" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="T280" t="n">
+        <v>382.51</v>
+      </c>
+      <c r="U280" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19717,7 +19786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22590,6 +22659,16 @@
       </c>
       <c r="B287" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -22758,28 +22837,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006079676020994171</v>
+        <v>0.001663230421492575</v>
       </c>
       <c r="J2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L2" t="n">
-        <v>4.434256893559585e-05</v>
+        <v>3.336579975421472e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.895430310548369</v>
+        <v>4.899246156367764</v>
       </c>
       <c r="N2" t="n">
-        <v>39.66382243526386</v>
+        <v>39.63489642225065</v>
       </c>
       <c r="O2" t="n">
-        <v>6.297922072816069</v>
+        <v>6.295625181207236</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6437155611868</v>
+        <v>381.6939046281496</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22836,28 +22915,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00898545082925902</v>
+        <v>0.005631718782790584</v>
       </c>
       <c r="J3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001213359553129401</v>
+        <v>4.796086648362063e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.359738546883583</v>
+        <v>4.357090272245568</v>
       </c>
       <c r="N3" t="n">
-        <v>31.66003064695738</v>
+        <v>31.61185245482237</v>
       </c>
       <c r="O3" t="n">
-        <v>5.626724681993724</v>
+        <v>5.622441858732055</v>
       </c>
       <c r="P3" t="n">
-        <v>383.8994324805188</v>
+        <v>383.9375447313012</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22914,28 +22993,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01437554705249001</v>
+        <v>0.01291934437559549</v>
       </c>
       <c r="J4" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K4" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003850568281712485</v>
+        <v>0.000313429221815209</v>
       </c>
       <c r="M4" t="n">
-        <v>3.71405929230691</v>
+        <v>3.70818466146819</v>
       </c>
       <c r="N4" t="n">
-        <v>25.52880412748043</v>
+        <v>25.44961396943765</v>
       </c>
       <c r="O4" t="n">
-        <v>5.052603697845343</v>
+        <v>5.044761041856953</v>
       </c>
       <c r="P4" t="n">
-        <v>384.8865979028771</v>
+        <v>384.9031463810628</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22992,28 +23071,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06683374092312414</v>
+        <v>0.0652003221856165</v>
       </c>
       <c r="J5" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K5" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006877004075391047</v>
+        <v>0.006597373658659089</v>
       </c>
       <c r="M5" t="n">
-        <v>4.106012692846998</v>
+        <v>4.100269501651564</v>
       </c>
       <c r="N5" t="n">
-        <v>30.69510318502788</v>
+        <v>30.60057457060688</v>
       </c>
       <c r="O5" t="n">
-        <v>5.540316162912355</v>
+        <v>5.531778608242279</v>
       </c>
       <c r="P5" t="n">
-        <v>380.8172432135789</v>
+        <v>380.8358055983175</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23070,28 +23149,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02878972116182376</v>
+        <v>-0.02358158522446027</v>
       </c>
       <c r="J6" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K6" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001192505143304268</v>
+        <v>0.0008031364404704755</v>
       </c>
       <c r="M6" t="n">
-        <v>4.379758983767578</v>
+        <v>4.383079796344934</v>
       </c>
       <c r="N6" t="n">
-        <v>33.034690972043</v>
+        <v>33.07376216633741</v>
       </c>
       <c r="O6" t="n">
-        <v>5.747581314957015</v>
+        <v>5.750979235429164</v>
       </c>
       <c r="P6" t="n">
-        <v>377.964486206146</v>
+        <v>377.905300266362</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23148,28 +23227,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02601048169436311</v>
+        <v>0.02995511376145187</v>
       </c>
       <c r="J7" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K7" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006434003720077186</v>
+        <v>0.0008586332810988084</v>
       </c>
       <c r="M7" t="n">
-        <v>4.977900328798079</v>
+        <v>4.977743427594986</v>
       </c>
       <c r="N7" t="n">
-        <v>50.00457804103397</v>
+        <v>49.91568604385167</v>
       </c>
       <c r="O7" t="n">
-        <v>7.071391520841846</v>
+        <v>7.065103399374398</v>
       </c>
       <c r="P7" t="n">
-        <v>373.2754914614143</v>
+        <v>373.2306641453073</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23226,28 +23305,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1040604961910888</v>
+        <v>-0.09589603329529617</v>
       </c>
       <c r="J8" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K8" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008596781281477894</v>
+        <v>0.007322434544917211</v>
       </c>
       <c r="M8" t="n">
-        <v>6.029335863391175</v>
+        <v>6.040055769451761</v>
       </c>
       <c r="N8" t="n">
-        <v>59.42374676901168</v>
+        <v>59.59775090619331</v>
       </c>
       <c r="O8" t="n">
-        <v>7.708679962808916</v>
+        <v>7.719957960131215</v>
       </c>
       <c r="P8" t="n">
-        <v>374.3932589690124</v>
+        <v>374.3004769419819</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23304,28 +23383,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1666199415327354</v>
+        <v>-0.1597583416974908</v>
       </c>
       <c r="J9" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K9" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02897901852344831</v>
+        <v>0.02675643073326683</v>
       </c>
       <c r="M9" t="n">
-        <v>5.295805954539037</v>
+        <v>5.310732816854058</v>
       </c>
       <c r="N9" t="n">
-        <v>44.26624635346084</v>
+        <v>44.38092274115346</v>
       </c>
       <c r="O9" t="n">
-        <v>6.653288386464308</v>
+        <v>6.661900835433793</v>
       </c>
       <c r="P9" t="n">
-        <v>375.7081130513075</v>
+        <v>375.6301369309537</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23382,28 +23461,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.138602076519174</v>
+        <v>-0.1304466950512634</v>
       </c>
       <c r="J10" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K10" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02224718705876705</v>
+        <v>0.01972928233062377</v>
       </c>
       <c r="M10" t="n">
-        <v>5.109638226172335</v>
+        <v>5.126469908290521</v>
       </c>
       <c r="N10" t="n">
-        <v>40.17605046708449</v>
+        <v>40.41818232930991</v>
       </c>
       <c r="O10" t="n">
-        <v>6.338458051220698</v>
+        <v>6.3575295775411</v>
       </c>
       <c r="P10" t="n">
-        <v>382.3329233759998</v>
+        <v>382.2402445515066</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23460,28 +23539,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07590657620094272</v>
+        <v>-0.07187445443934967</v>
       </c>
       <c r="J11" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K11" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002914067166872369</v>
+        <v>0.002632302312017609</v>
       </c>
       <c r="M11" t="n">
-        <v>7.792054526377931</v>
+        <v>7.78595336222568</v>
       </c>
       <c r="N11" t="n">
-        <v>93.81356431331363</v>
+        <v>93.57170249550349</v>
       </c>
       <c r="O11" t="n">
-        <v>9.685740256341465</v>
+        <v>9.673246740133505</v>
       </c>
       <c r="P11" t="n">
-        <v>382.6611375682104</v>
+        <v>382.6153160077416</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -23542,28 +23621,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05134012661039722</v>
+        <v>0.0510443335164807</v>
       </c>
       <c r="J12" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K12" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003183683299864182</v>
+        <v>0.003173113494124191</v>
       </c>
       <c r="M12" t="n">
-        <v>4.959642601107828</v>
+        <v>4.942952012845402</v>
       </c>
       <c r="N12" t="n">
-        <v>39.60686283656206</v>
+        <v>39.46334814243405</v>
       </c>
       <c r="O12" t="n">
-        <v>6.293398353557643</v>
+        <v>6.281986003043468</v>
       </c>
       <c r="P12" t="n">
-        <v>372.4929372952741</v>
+        <v>372.4962889218344</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -23624,28 +23703,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1384629398608674</v>
+        <v>-0.1378003175162871</v>
       </c>
       <c r="J13" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K13" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03311336226225381</v>
+        <v>0.03306543161767828</v>
       </c>
       <c r="M13" t="n">
-        <v>3.946697540700812</v>
+        <v>3.935526051542569</v>
       </c>
       <c r="N13" t="n">
-        <v>26.62302179608561</v>
+        <v>26.52911165757938</v>
       </c>
       <c r="O13" t="n">
-        <v>5.159750167991239</v>
+        <v>5.150641868503321</v>
       </c>
       <c r="P13" t="n">
-        <v>362.0432019741239</v>
+        <v>362.0356459159306</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23702,28 +23781,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1650776137627765</v>
+        <v>-0.1694598135896782</v>
       </c>
       <c r="J14" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K14" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03166364148312761</v>
+        <v>0.03348409531700169</v>
       </c>
       <c r="M14" t="n">
-        <v>4.991579054613956</v>
+        <v>4.996154238038963</v>
       </c>
       <c r="N14" t="n">
-        <v>39.65660610797983</v>
+        <v>39.62595663668973</v>
       </c>
       <c r="O14" t="n">
-        <v>6.29734913340366</v>
+        <v>6.29491514134144</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0948871072264</v>
+        <v>364.1446870007383</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23780,28 +23859,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1317930994348379</v>
+        <v>-0.1300097054790482</v>
       </c>
       <c r="J15" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K15" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0253002295500695</v>
+        <v>0.0248206479244949</v>
       </c>
       <c r="M15" t="n">
-        <v>4.365174742277069</v>
+        <v>4.355862014256569</v>
       </c>
       <c r="N15" t="n">
-        <v>31.84238177039881</v>
+        <v>31.74671605311728</v>
       </c>
       <c r="O15" t="n">
-        <v>5.64290543695345</v>
+        <v>5.634422424092578</v>
       </c>
       <c r="P15" t="n">
-        <v>362.2695109641991</v>
+        <v>362.2492442414124</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23858,28 +23937,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08595337818258507</v>
+        <v>-0.08371940328242047</v>
       </c>
       <c r="J16" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K16" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01291199808226795</v>
+        <v>0.01234415665342758</v>
       </c>
       <c r="M16" t="n">
-        <v>4.039008575742403</v>
+        <v>4.032133750124842</v>
       </c>
       <c r="N16" t="n">
-        <v>26.87584453338445</v>
+        <v>26.8084890350098</v>
       </c>
       <c r="O16" t="n">
-        <v>5.184191791724574</v>
+        <v>5.177691477387369</v>
       </c>
       <c r="P16" t="n">
-        <v>360.5795420968428</v>
+        <v>360.5541549131152</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23936,28 +24015,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.07435559031187181</v>
+        <v>-0.07174240993940503</v>
       </c>
       <c r="J17" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K17" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0119243595419013</v>
+        <v>0.01118037035962183</v>
       </c>
       <c r="M17" t="n">
-        <v>3.358892335554435</v>
+        <v>3.356650486854047</v>
       </c>
       <c r="N17" t="n">
-        <v>21.79998433109894</v>
+        <v>21.76149297073992</v>
       </c>
       <c r="O17" t="n">
-        <v>4.669045334016253</v>
+        <v>4.664921539612421</v>
       </c>
       <c r="P17" t="n">
-        <v>363.5996574533553</v>
+        <v>363.5699609289117</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24014,28 +24093,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01766090688346728</v>
+        <v>0.02224239968484696</v>
       </c>
       <c r="J18" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K18" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0003870453327462497</v>
+        <v>0.0006168468631696511</v>
       </c>
       <c r="M18" t="n">
-        <v>4.328644213589252</v>
+        <v>4.331292794626858</v>
       </c>
       <c r="N18" t="n">
-        <v>38.33273810848957</v>
+        <v>38.31720481737243</v>
       </c>
       <c r="O18" t="n">
-        <v>6.191343804739773</v>
+        <v>6.190089241470791</v>
       </c>
       <c r="P18" t="n">
-        <v>366.387495961345</v>
+        <v>366.3354312763359</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24092,28 +24171,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0302601430135956</v>
+        <v>-0.02435512931026502</v>
       </c>
       <c r="J19" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K19" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001131524343822354</v>
+        <v>0.0007354423516442443</v>
       </c>
       <c r="M19" t="n">
-        <v>4.564804144705732</v>
+        <v>4.573216710169322</v>
       </c>
       <c r="N19" t="n">
-        <v>38.46450581898991</v>
+        <v>38.52907683845712</v>
       </c>
       <c r="O19" t="n">
-        <v>6.201975960852308</v>
+        <v>6.207179459179275</v>
       </c>
       <c r="P19" t="n">
-        <v>370.7753882824928</v>
+        <v>370.7082829323882</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24170,28 +24249,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1126933871453226</v>
+        <v>-0.1077767724699786</v>
       </c>
       <c r="J20" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K20" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02503458566080219</v>
+        <v>0.02299698120942117</v>
       </c>
       <c r="M20" t="n">
-        <v>3.652697655255968</v>
+        <v>3.65898355417432</v>
       </c>
       <c r="N20" t="n">
-        <v>23.5352852458462</v>
+        <v>23.59126878922326</v>
       </c>
       <c r="O20" t="n">
-        <v>4.851317887527697</v>
+        <v>4.857084391816067</v>
       </c>
       <c r="P20" t="n">
-        <v>379.1874635673599</v>
+        <v>379.1315905134275</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24229,7 +24308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U279"/>
+  <dimension ref="A1:U280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54057,6 +54136,113 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>-35.67350731175671,174.5082962400339</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>-35.67423144727564,174.50841144805187</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-35.67494865210114,174.50852409232633</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>-35.675666312667445,174.5086325872432</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>-35.676380957294406,174.50881380901353</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-35.67710840596424,174.5089066142989</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-35.67782321013075,174.50908586730816</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-35.678542493125704,174.50921367896106</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-35.67918929988455,174.5094726395686</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-35.67976817448843,174.50994864803394</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-35.68048471714179,174.51015284318402</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-35.68123135268176,174.5099911408294</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-35.68196466066801,174.51005910112008</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-35.682671667236804,174.51029833514912</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-35.68338719110274,174.51047353466546</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>-35.684101248726556,174.51065980228572</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>-35.68480330681031,174.51088501082353</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>-35.6854548487567,174.51119360231357</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>-35.68605457865968,174.5116760771468</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U280"/>
+  <dimension ref="A1:U281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19772,6 +19772,75 @@
       <c r="U280" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>375.13</v>
+      </c>
+      <c r="C281" t="n">
+        <v>377.33</v>
+      </c>
+      <c r="D281" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="E281" t="n">
+        <v>380.93</v>
+      </c>
+      <c r="F281" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="G281" t="n">
+        <v>381.78</v>
+      </c>
+      <c r="H281" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="I281" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="J281" t="n">
+        <v>389.45</v>
+      </c>
+      <c r="K281" t="n">
+        <v>390.57</v>
+      </c>
+      <c r="L281" t="n">
+        <v>379.02</v>
+      </c>
+      <c r="M281" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="N281" t="n">
+        <v>351.72</v>
+      </c>
+      <c r="O281" t="n">
+        <v>364.93</v>
+      </c>
+      <c r="P281" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>367.38</v>
+      </c>
+      <c r="R281" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="S281" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="T281" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19786,7 +19855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22669,6 +22738,16 @@
       </c>
       <c r="B288" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -22837,28 +22916,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001663230421492575</v>
+        <v>-0.003513988951811752</v>
       </c>
       <c r="J2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L2" t="n">
-        <v>3.336579975421472e-06</v>
+        <v>1.495929078509928e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.899246156367764</v>
+        <v>4.906396509504243</v>
       </c>
       <c r="N2" t="n">
-        <v>39.63489642225065</v>
+        <v>39.64754267182378</v>
       </c>
       <c r="O2" t="n">
-        <v>6.295625181207236</v>
+        <v>6.296629469154412</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6939046281496</v>
+        <v>381.7530837665397</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22915,28 +22994,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005631718782790584</v>
+        <v>0.0003378741173060536</v>
       </c>
       <c r="J3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L3" t="n">
-        <v>4.796086648362063e-05</v>
+        <v>1.73192633012853e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>4.357090272245568</v>
+        <v>4.36263026586899</v>
       </c>
       <c r="N3" t="n">
-        <v>31.61185245482237</v>
+        <v>31.66017786838222</v>
       </c>
       <c r="O3" t="n">
-        <v>5.622441858732055</v>
+        <v>5.626737764316213</v>
       </c>
       <c r="P3" t="n">
-        <v>383.9375447313012</v>
+        <v>383.9980569760962</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22993,28 +23072,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01291934437559549</v>
+        <v>0.01087053244984594</v>
       </c>
       <c r="J4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000313429221815209</v>
+        <v>0.0002235613781076395</v>
       </c>
       <c r="M4" t="n">
-        <v>3.70818466146819</v>
+        <v>3.705223737683094</v>
       </c>
       <c r="N4" t="n">
-        <v>25.44961396943765</v>
+        <v>25.38287119781276</v>
       </c>
       <c r="O4" t="n">
-        <v>5.044761041856953</v>
+        <v>5.038141641301161</v>
       </c>
       <c r="P4" t="n">
-        <v>384.9031463810628</v>
+        <v>384.926565694742</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23071,28 +23150,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0652003221856165</v>
+        <v>0.06392113913093136</v>
       </c>
       <c r="J5" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K5" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006597373658659089</v>
+        <v>0.006393323694792397</v>
       </c>
       <c r="M5" t="n">
-        <v>4.100269501651564</v>
+        <v>4.092536361423108</v>
       </c>
       <c r="N5" t="n">
-        <v>30.60057457060688</v>
+        <v>30.50070039013666</v>
       </c>
       <c r="O5" t="n">
-        <v>5.531778608242279</v>
+        <v>5.522743918573146</v>
       </c>
       <c r="P5" t="n">
-        <v>380.8358055983175</v>
+        <v>380.8504275305868</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23149,28 +23228,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02358158522446027</v>
+        <v>-0.01801888423264126</v>
       </c>
       <c r="J6" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K6" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008031364404704755</v>
+        <v>0.0004704516859553864</v>
       </c>
       <c r="M6" t="n">
-        <v>4.383079796344934</v>
+        <v>4.387442122202096</v>
       </c>
       <c r="N6" t="n">
-        <v>33.07376216633741</v>
+        <v>33.13365844246994</v>
       </c>
       <c r="O6" t="n">
-        <v>5.750979235429164</v>
+        <v>5.756184364878346</v>
       </c>
       <c r="P6" t="n">
-        <v>377.905300266362</v>
+        <v>377.8417148109117</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23227,28 +23306,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02995511376145187</v>
+        <v>0.03602739937690681</v>
       </c>
       <c r="J7" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K7" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008586332810988084</v>
+        <v>0.001246595584946331</v>
       </c>
       <c r="M7" t="n">
-        <v>4.977743427594986</v>
+        <v>4.986829424912016</v>
       </c>
       <c r="N7" t="n">
-        <v>49.91568604385167</v>
+        <v>49.94954182024863</v>
       </c>
       <c r="O7" t="n">
-        <v>7.065103399374398</v>
+        <v>7.067498979147336</v>
       </c>
       <c r="P7" t="n">
-        <v>373.2306641453073</v>
+        <v>373.1612537910476</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23305,28 +23384,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09589603329529617</v>
+        <v>-0.08753489080496693</v>
       </c>
       <c r="J8" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K8" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007322434544917211</v>
+        <v>0.006118187264533614</v>
       </c>
       <c r="M8" t="n">
-        <v>6.040055769451761</v>
+        <v>6.050982320304693</v>
       </c>
       <c r="N8" t="n">
-        <v>59.59775090619331</v>
+        <v>59.78708223300796</v>
       </c>
       <c r="O8" t="n">
-        <v>7.719957960131215</v>
+        <v>7.732210695073432</v>
       </c>
       <c r="P8" t="n">
-        <v>374.3004769419819</v>
+        <v>374.2049033970233</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23383,28 +23462,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1597583416974908</v>
+        <v>-0.1518387551632583</v>
       </c>
       <c r="J9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02675643073326683</v>
+        <v>0.02423656929301576</v>
       </c>
       <c r="M9" t="n">
-        <v>5.310732816854058</v>
+        <v>5.330201760645778</v>
       </c>
       <c r="N9" t="n">
-        <v>44.38092274115346</v>
+        <v>44.58324285810221</v>
       </c>
       <c r="O9" t="n">
-        <v>6.661900835433793</v>
+        <v>6.677068432935386</v>
       </c>
       <c r="P9" t="n">
-        <v>375.6301369309537</v>
+        <v>375.5396106708692</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23461,28 +23540,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1304466950512634</v>
+        <v>-0.1220881650875599</v>
       </c>
       <c r="J10" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K10" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01972928233062377</v>
+        <v>0.01729684099832629</v>
       </c>
       <c r="M10" t="n">
-        <v>5.126469908290521</v>
+        <v>5.143541164476548</v>
       </c>
       <c r="N10" t="n">
-        <v>40.41818232930991</v>
+        <v>40.67576082360546</v>
       </c>
       <c r="O10" t="n">
-        <v>6.3575295775411</v>
+        <v>6.377755155507733</v>
       </c>
       <c r="P10" t="n">
-        <v>382.2402445515066</v>
+        <v>382.1447008695041</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23539,28 +23618,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07187445443934967</v>
+        <v>-0.06415242992383698</v>
       </c>
       <c r="J11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002632302312017609</v>
+        <v>0.002107934576777604</v>
       </c>
       <c r="M11" t="n">
-        <v>7.78595336222568</v>
+        <v>7.799293494214598</v>
       </c>
       <c r="N11" t="n">
-        <v>93.57170249550349</v>
+        <v>93.58056359479596</v>
       </c>
       <c r="O11" t="n">
-        <v>9.673246740133505</v>
+        <v>9.673704750238967</v>
       </c>
       <c r="P11" t="n">
-        <v>382.6153160077416</v>
+        <v>382.5270480158903</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -23621,28 +23700,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0510443335164807</v>
+        <v>0.0551131660395158</v>
       </c>
       <c r="J12" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K12" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003173113494124191</v>
+        <v>0.003719055112070269</v>
       </c>
       <c r="M12" t="n">
-        <v>4.942952012845402</v>
+        <v>4.944008559002994</v>
       </c>
       <c r="N12" t="n">
-        <v>39.46334814243405</v>
+        <v>39.4160483770603</v>
       </c>
       <c r="O12" t="n">
-        <v>6.281986003043468</v>
+        <v>6.278220159970523</v>
       </c>
       <c r="P12" t="n">
-        <v>372.4962889218344</v>
+        <v>372.4499114003397</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -23703,28 +23782,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1378003175162871</v>
+        <v>-0.13491904582472</v>
       </c>
       <c r="J13" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K13" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03306543161767828</v>
+        <v>0.03194099749241941</v>
       </c>
       <c r="M13" t="n">
-        <v>3.935526051542569</v>
+        <v>3.93467379620051</v>
       </c>
       <c r="N13" t="n">
-        <v>26.52911165757938</v>
+        <v>26.48110968449924</v>
       </c>
       <c r="O13" t="n">
-        <v>5.150641868503321</v>
+        <v>5.145979953759949</v>
       </c>
       <c r="P13" t="n">
-        <v>362.0356459159306</v>
+        <v>362.0025959914839</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23781,28 +23860,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1694598135896782</v>
+        <v>-0.1756692338846123</v>
       </c>
       <c r="J14" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K14" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03348409531700169</v>
+        <v>0.03598722146371425</v>
       </c>
       <c r="M14" t="n">
-        <v>4.996154238038963</v>
+        <v>5.00988696188655</v>
       </c>
       <c r="N14" t="n">
-        <v>39.62595663668973</v>
+        <v>39.70625081984716</v>
       </c>
       <c r="O14" t="n">
-        <v>6.29491514134144</v>
+        <v>6.301289615614185</v>
       </c>
       <c r="P14" t="n">
-        <v>364.1446870007383</v>
+        <v>364.2156648976479</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23859,28 +23938,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1300097054790482</v>
+        <v>-0.1252122380045752</v>
       </c>
       <c r="J15" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K15" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0248206479244949</v>
+        <v>0.0231575212336157</v>
       </c>
       <c r="M15" t="n">
-        <v>4.355862014256569</v>
+        <v>4.356995879955713</v>
       </c>
       <c r="N15" t="n">
-        <v>31.74671605311728</v>
+        <v>31.76574278557198</v>
       </c>
       <c r="O15" t="n">
-        <v>5.634422424092578</v>
+        <v>5.636110607996615</v>
       </c>
       <c r="P15" t="n">
-        <v>362.2492442414124</v>
+        <v>362.1944059254898</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23937,28 +24016,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08371940328242047</v>
+        <v>-0.08070358958575967</v>
       </c>
       <c r="J16" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K16" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01234415665342758</v>
+        <v>0.01155323553032339</v>
       </c>
       <c r="M16" t="n">
-        <v>4.032133750124842</v>
+        <v>4.027981249469943</v>
       </c>
       <c r="N16" t="n">
-        <v>26.8084890350098</v>
+        <v>26.7650681631229</v>
       </c>
       <c r="O16" t="n">
-        <v>5.177691477387369</v>
+        <v>5.173496705625983</v>
       </c>
       <c r="P16" t="n">
-        <v>360.5541549131152</v>
+        <v>360.5196821115503</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24015,28 +24094,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.07174240993940503</v>
+        <v>-0.06726780556289229</v>
       </c>
       <c r="J17" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K17" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01118037035962183</v>
+        <v>0.009871953881507078</v>
       </c>
       <c r="M17" t="n">
-        <v>3.356650486854047</v>
+        <v>3.362385551280855</v>
       </c>
       <c r="N17" t="n">
-        <v>21.76149297073992</v>
+        <v>21.79895916243128</v>
       </c>
       <c r="O17" t="n">
-        <v>4.664921539612421</v>
+        <v>4.668935549183698</v>
       </c>
       <c r="P17" t="n">
-        <v>363.5699609289117</v>
+        <v>363.5188131577734</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24093,28 +24172,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02224239968484696</v>
+        <v>0.028258141154857</v>
       </c>
       <c r="J18" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K18" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0006168468631696511</v>
+        <v>0.0009981245796824023</v>
       </c>
       <c r="M18" t="n">
-        <v>4.331292794626858</v>
+        <v>4.339259410168698</v>
       </c>
       <c r="N18" t="n">
-        <v>38.31720481737243</v>
+        <v>38.38855156669399</v>
       </c>
       <c r="O18" t="n">
-        <v>6.190089241470791</v>
+        <v>6.195849543581089</v>
       </c>
       <c r="P18" t="n">
-        <v>366.3354312763359</v>
+        <v>366.2666672601135</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24171,28 +24250,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.02435512931026502</v>
+        <v>-0.01502071826321303</v>
       </c>
       <c r="J19" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K19" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0007354423516442443</v>
+        <v>0.0002785639611836421</v>
       </c>
       <c r="M19" t="n">
-        <v>4.573216710169322</v>
+        <v>4.595931617212424</v>
       </c>
       <c r="N19" t="n">
-        <v>38.52907683845712</v>
+        <v>38.89273355295597</v>
       </c>
       <c r="O19" t="n">
-        <v>6.207179459179275</v>
+        <v>6.23640389591277</v>
       </c>
       <c r="P19" t="n">
-        <v>370.7082829323882</v>
+        <v>370.6015842659202</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24249,28 +24328,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1077767724699786</v>
+        <v>-0.09961456091889724</v>
       </c>
       <c r="J20" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K20" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02299698120942117</v>
+        <v>0.01956041894991645</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65898355417432</v>
+        <v>3.679170011884238</v>
       </c>
       <c r="N20" t="n">
-        <v>23.59126878922326</v>
+        <v>23.89028475140516</v>
       </c>
       <c r="O20" t="n">
-        <v>4.857084391816067</v>
+        <v>4.887768893002733</v>
       </c>
       <c r="P20" t="n">
-        <v>379.1315905134275</v>
+        <v>379.0382908843947</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24308,7 +24387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U280"/>
+  <dimension ref="A1:U281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54243,6 +54322,113 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>-35.67350816534951,174.5082850202751</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>-35.67423354780635,174.50838383839923</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-35.674949555576,174.50851565799067</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-35.67566564286264,174.50863737844665</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-35.67638017064921,174.50881936032965</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-35.67710411655805,174.50893676224453</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-35.67782269141998,174.50908945731453</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-35.67854003804567,174.50922885088673</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-35.6791880782461,174.50947596386135</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-35.67974707869629,174.50999431620752</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-35.68047535556501,174.51021307888163</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-35.68122946089568,174.51002198970198</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-35.68196834245789,174.5100328590936</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-35.68266481187998,174.51034003462323</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-35.68338548769579,174.5104844969276</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>-35.6840975784186,174.51068593531417</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>-35.68479922161282,174.51090528425746</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>-35.68543848293733,174.51123837158738</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>-35.686035697273226,174.51171604570666</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U281"/>
+  <dimension ref="A1:U283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19841,6 +19841,144 @@
       <c r="U281" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>375.58</v>
+      </c>
+      <c r="C282" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="D282" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="E282" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="F282" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="G282" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="H282" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="I282" t="n">
+        <v>381.37</v>
+      </c>
+      <c r="J282" t="n">
+        <v>389.55</v>
+      </c>
+      <c r="K282" t="n">
+        <v>390.14</v>
+      </c>
+      <c r="L282" t="n">
+        <v>379.28</v>
+      </c>
+      <c r="M282" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="N282" t="n">
+        <v>353.73</v>
+      </c>
+      <c r="O282" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="P282" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="R282" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="S282" t="n">
+        <v>380.25</v>
+      </c>
+      <c r="T282" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>377.02</v>
+      </c>
+      <c r="C283" t="n">
+        <v>376.93</v>
+      </c>
+      <c r="D283" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="E283" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="F283" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="G283" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="H283" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="I283" t="n">
+        <v>380.39</v>
+      </c>
+      <c r="J283" t="n">
+        <v>388.74</v>
+      </c>
+      <c r="K283" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="L283" t="n">
+        <v>385.09</v>
+      </c>
+      <c r="M283" t="n">
+        <v>362.57</v>
+      </c>
+      <c r="N283" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="O283" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="P283" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="R283" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="S283" t="n">
+        <v>379.11</v>
+      </c>
+      <c r="T283" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19855,7 +19993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22748,6 +22886,26 @@
       </c>
       <c r="B289" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -22916,28 +23074,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.003513988951811752</v>
+        <v>-0.01177481601886301</v>
       </c>
       <c r="J2" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K2" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L2" t="n">
-        <v>1.495929078509928e-05</v>
+        <v>0.0001698551755150435</v>
       </c>
       <c r="M2" t="n">
-        <v>4.906396509504243</v>
+        <v>4.910897496080266</v>
       </c>
       <c r="N2" t="n">
-        <v>39.64754267182378</v>
+        <v>39.56924108547089</v>
       </c>
       <c r="O2" t="n">
-        <v>6.296629469154412</v>
+        <v>6.290408658065936</v>
       </c>
       <c r="P2" t="n">
-        <v>381.7530837665397</v>
+        <v>381.8477668481293</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22994,28 +23152,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003378741173060536</v>
+        <v>-0.01004070481035073</v>
       </c>
       <c r="J3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L3" t="n">
-        <v>1.73192633012853e-07</v>
+        <v>0.0001539261284816407</v>
       </c>
       <c r="M3" t="n">
-        <v>4.36263026586899</v>
+        <v>4.372691261250619</v>
       </c>
       <c r="N3" t="n">
-        <v>31.66017786838222</v>
+        <v>31.75054735916888</v>
       </c>
       <c r="O3" t="n">
-        <v>5.626737764316213</v>
+        <v>5.63476240485514</v>
       </c>
       <c r="P3" t="n">
-        <v>383.9980569760962</v>
+        <v>384.1170407285041</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23072,28 +23230,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01087053244984594</v>
+        <v>0.004280133672658685</v>
       </c>
       <c r="J4" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K4" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002235613781076395</v>
+        <v>3.505859311991877e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.705223737683094</v>
+        <v>3.711784071726039</v>
       </c>
       <c r="N4" t="n">
-        <v>25.38287119781276</v>
+        <v>25.33418711231472</v>
       </c>
       <c r="O4" t="n">
-        <v>5.038141641301161</v>
+        <v>5.033307770474077</v>
       </c>
       <c r="P4" t="n">
-        <v>384.926565694742</v>
+        <v>385.0021337620487</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23150,28 +23308,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06392113913093136</v>
+        <v>0.05780543178890189</v>
       </c>
       <c r="J5" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K5" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006393323694792397</v>
+        <v>0.005298916990456926</v>
       </c>
       <c r="M5" t="n">
-        <v>4.092536361423108</v>
+        <v>4.096062229993032</v>
       </c>
       <c r="N5" t="n">
-        <v>30.50070039013666</v>
+        <v>30.41198673893595</v>
       </c>
       <c r="O5" t="n">
-        <v>5.522743918573146</v>
+        <v>5.514706405506638</v>
       </c>
       <c r="P5" t="n">
-        <v>380.8504275305868</v>
+        <v>380.9205717066847</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23228,28 +23386,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01801888423264126</v>
+        <v>-0.01224127413067524</v>
       </c>
       <c r="J6" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K6" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004704516859553864</v>
+        <v>0.000219961879594055</v>
       </c>
       <c r="M6" t="n">
-        <v>4.387442122202096</v>
+        <v>4.376992304631526</v>
       </c>
       <c r="N6" t="n">
-        <v>33.13365844246994</v>
+        <v>33.02267915955773</v>
       </c>
       <c r="O6" t="n">
-        <v>5.756184364878346</v>
+        <v>5.746536274971014</v>
       </c>
       <c r="P6" t="n">
-        <v>377.8417148109117</v>
+        <v>377.7755250799579</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23306,28 +23464,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03602739937690681</v>
+        <v>0.04479860310041603</v>
       </c>
       <c r="J7" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K7" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001246595584946331</v>
+        <v>0.001948609636412635</v>
       </c>
       <c r="M7" t="n">
-        <v>4.986829424912016</v>
+        <v>4.991165631876927</v>
       </c>
       <c r="N7" t="n">
-        <v>49.94954182024863</v>
+        <v>49.83781814112839</v>
       </c>
       <c r="O7" t="n">
-        <v>7.067498979147336</v>
+        <v>7.059590508034329</v>
       </c>
       <c r="P7" t="n">
-        <v>373.1612537910476</v>
+        <v>373.0607389931098</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23384,28 +23542,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08753489080496693</v>
+        <v>-0.07336289435474355</v>
       </c>
       <c r="J8" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K8" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006118187264533614</v>
+        <v>0.004332980249632579</v>
       </c>
       <c r="M8" t="n">
-        <v>6.050982320304693</v>
+        <v>6.062376947926522</v>
       </c>
       <c r="N8" t="n">
-        <v>59.78708223300796</v>
+        <v>59.96286087043393</v>
       </c>
       <c r="O8" t="n">
-        <v>7.732210695073432</v>
+        <v>7.743569000818288</v>
       </c>
       <c r="P8" t="n">
-        <v>374.2049033970233</v>
+        <v>374.0424714140453</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23462,28 +23620,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1518387551632583</v>
+        <v>-0.1373845172135928</v>
       </c>
       <c r="J9" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K9" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02423656929301576</v>
+        <v>0.01998364949444076</v>
       </c>
       <c r="M9" t="n">
-        <v>5.330201760645778</v>
+        <v>5.362318704056776</v>
       </c>
       <c r="N9" t="n">
-        <v>44.58324285810221</v>
+        <v>44.87827136002507</v>
       </c>
       <c r="O9" t="n">
-        <v>6.677068432935386</v>
+        <v>6.699124671180935</v>
       </c>
       <c r="P9" t="n">
-        <v>375.5396106708692</v>
+        <v>375.3739234202064</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23540,28 +23698,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1220881650875599</v>
+        <v>-0.1063018832357741</v>
       </c>
       <c r="J10" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K10" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01729684099832629</v>
+        <v>0.01315012436146679</v>
       </c>
       <c r="M10" t="n">
-        <v>5.143541164476548</v>
+        <v>5.17340558067267</v>
       </c>
       <c r="N10" t="n">
-        <v>40.67576082360546</v>
+        <v>41.11546122334424</v>
       </c>
       <c r="O10" t="n">
-        <v>6.377755155507733</v>
+        <v>6.412133905599932</v>
       </c>
       <c r="P10" t="n">
-        <v>382.1447008695041</v>
+        <v>381.963741770885</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23618,28 +23776,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06415242992383698</v>
+        <v>-0.04678323688196376</v>
       </c>
       <c r="J11" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K11" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002107934576777604</v>
+        <v>0.00112975477662236</v>
       </c>
       <c r="M11" t="n">
-        <v>7.799293494214598</v>
+        <v>7.8360599294974</v>
       </c>
       <c r="N11" t="n">
-        <v>93.58056359479596</v>
+        <v>93.82259539791693</v>
       </c>
       <c r="O11" t="n">
-        <v>9.673704750238967</v>
+        <v>9.686206450304315</v>
       </c>
       <c r="P11" t="n">
-        <v>382.5270480158903</v>
+        <v>382.3278911594139</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -23700,28 +23858,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0551131660395158</v>
+        <v>0.06793098147186746</v>
       </c>
       <c r="J12" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K12" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003719055112070269</v>
+        <v>0.005655015153556375</v>
       </c>
       <c r="M12" t="n">
-        <v>4.944008559002994</v>
+        <v>4.968060409146224</v>
       </c>
       <c r="N12" t="n">
-        <v>39.4160483770603</v>
+        <v>39.6737106798854</v>
       </c>
       <c r="O12" t="n">
-        <v>6.278220159970523</v>
+        <v>6.298707064143038</v>
       </c>
       <c r="P12" t="n">
-        <v>372.4499114003397</v>
+        <v>372.3033188063537</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -23782,28 +23940,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.13491904582472</v>
+        <v>-0.1279129893098621</v>
       </c>
       <c r="J13" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K13" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03194099749241941</v>
+        <v>0.02911229935997484</v>
       </c>
       <c r="M13" t="n">
-        <v>3.93467379620051</v>
+        <v>3.938546703177838</v>
       </c>
       <c r="N13" t="n">
-        <v>26.48110968449924</v>
+        <v>26.43547085604415</v>
       </c>
       <c r="O13" t="n">
-        <v>5.145979953759949</v>
+        <v>5.141543625803846</v>
       </c>
       <c r="P13" t="n">
-        <v>362.0025959914839</v>
+        <v>361.9220068758826</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23860,28 +24018,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1756692338846123</v>
+        <v>-0.1836492213698742</v>
       </c>
       <c r="J14" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K14" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03598722146371425</v>
+        <v>0.0396434054109146</v>
       </c>
       <c r="M14" t="n">
-        <v>5.00988696188655</v>
+        <v>5.014792086861561</v>
       </c>
       <c r="N14" t="n">
-        <v>39.70625081984716</v>
+        <v>39.61336819267564</v>
       </c>
       <c r="O14" t="n">
-        <v>6.301289615614185</v>
+        <v>6.293915172027316</v>
       </c>
       <c r="P14" t="n">
-        <v>364.2156648976479</v>
+        <v>364.3071304659313</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23938,28 +24096,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1252122380045752</v>
+        <v>-0.1157267750628597</v>
       </c>
       <c r="J15" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K15" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0231575212336157</v>
+        <v>0.02000718703143456</v>
       </c>
       <c r="M15" t="n">
-        <v>4.356995879955713</v>
+        <v>4.358706463530633</v>
       </c>
       <c r="N15" t="n">
-        <v>31.76574278557198</v>
+        <v>31.80581870371724</v>
       </c>
       <c r="O15" t="n">
-        <v>5.636110607996615</v>
+        <v>5.639664768735571</v>
       </c>
       <c r="P15" t="n">
-        <v>362.1944059254898</v>
+        <v>362.0856819737992</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24016,28 +24174,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08070358958575967</v>
+        <v>-0.07780106395569293</v>
       </c>
       <c r="J16" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K16" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01155323553032339</v>
+        <v>0.01091127933139824</v>
       </c>
       <c r="M16" t="n">
-        <v>4.027981249469943</v>
+        <v>4.009183936406478</v>
       </c>
       <c r="N16" t="n">
-        <v>26.7650681631229</v>
+        <v>26.60312568850077</v>
       </c>
       <c r="O16" t="n">
-        <v>5.173496705625983</v>
+        <v>5.157821796892636</v>
       </c>
       <c r="P16" t="n">
-        <v>360.5196821115503</v>
+        <v>360.4864236280476</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24094,28 +24252,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06726780556289229</v>
+        <v>-0.05944048028311513</v>
       </c>
       <c r="J17" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K17" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009871953881507078</v>
+        <v>0.00778777850080814</v>
       </c>
       <c r="M17" t="n">
-        <v>3.362385551280855</v>
+        <v>3.369863422103546</v>
       </c>
       <c r="N17" t="n">
-        <v>21.79895916243128</v>
+        <v>21.82516922255089</v>
       </c>
       <c r="O17" t="n">
-        <v>4.668935549183698</v>
+        <v>4.671741562046309</v>
       </c>
       <c r="P17" t="n">
-        <v>363.5188131577734</v>
+        <v>363.4290953870899</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24172,28 +24330,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.028258141154857</v>
+        <v>0.03972564440908979</v>
       </c>
       <c r="J18" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K18" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0009981245796824023</v>
+        <v>0.001983416609215083</v>
       </c>
       <c r="M18" t="n">
-        <v>4.339259410168698</v>
+        <v>4.353190744368974</v>
       </c>
       <c r="N18" t="n">
-        <v>38.38855156669399</v>
+        <v>38.50062080513025</v>
       </c>
       <c r="O18" t="n">
-        <v>6.195849543581089</v>
+        <v>6.204886848696779</v>
       </c>
       <c r="P18" t="n">
-        <v>366.2666672601135</v>
+        <v>366.1352149437311</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24250,28 +24408,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01502071826321303</v>
+        <v>-0.0004175969203642084</v>
       </c>
       <c r="J19" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K19" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0002785639611836421</v>
+        <v>2.15462700570157e-07</v>
       </c>
       <c r="M19" t="n">
-        <v>4.595931617212424</v>
+        <v>4.623949373754232</v>
       </c>
       <c r="N19" t="n">
-        <v>38.89273355295597</v>
+        <v>39.24139155978418</v>
       </c>
       <c r="O19" t="n">
-        <v>6.23640389591277</v>
+        <v>6.264294977073172</v>
       </c>
       <c r="P19" t="n">
-        <v>370.6015842659202</v>
+        <v>370.4341921039756</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24328,28 +24486,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.09961456091889724</v>
+        <v>-0.08598169473415912</v>
       </c>
       <c r="J20" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K20" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01956041894991645</v>
+        <v>0.01455443633949149</v>
       </c>
       <c r="M20" t="n">
-        <v>3.679170011884238</v>
+        <v>3.710161291747044</v>
       </c>
       <c r="N20" t="n">
-        <v>23.89028475140516</v>
+        <v>24.26896573465774</v>
       </c>
       <c r="O20" t="n">
-        <v>4.887768893002733</v>
+        <v>4.926354203126054</v>
       </c>
       <c r="P20" t="n">
-        <v>379.0382908843947</v>
+        <v>378.8820286471527</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24387,7 +24545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U281"/>
+  <dimension ref="A1:U283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54429,6 +54587,220 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>-35.67350778876458,174.50828997016873</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>-35.67423330511587,174.50838702835918</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>-35.674950564651134,174.50850623782333</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-35.67566673890676,174.50862953829548</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-35.67638222209595,174.5088048833678</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-35.67710470499688,174.50893262642546</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-35.67782264426446,174.50908978367872</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-35.678540266017464,174.5092274420651</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-35.6791877080526,174.50947697122274</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-35.679748988421316,174.50999018203703</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-35.680474917003906,174.51021590073375</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-35.681228609589375,174.51003587169407</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-35.68196527175386,174.5100547455972</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-35.68266352983763,174.51034783296558</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>-35.68338757900717,174.51047103830868</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>-35.68409763959043,174.5106854997637</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>-35.68479887577585,174.5109070005269</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>-35.68544485971122,174.5112209277059</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>-35.68603818166692,174.5117107866867</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>-35.673506583691434,174.50830580982796</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>-35.674233882551704,174.50837943845443</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>-35.67495250066531,174.50848816424573</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>-35.67567168632186,174.50859414872127</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>-35.67638817590912,174.50876286751898</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-35.677109598324925,174.50889823382246</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-35.67782698256951,174.5090597581694</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-35.67854198457355,174.50921682171716</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-35.679190706619615,174.509468811595</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>-35.67973171206658,174.51002758185123</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>-35.68046511683335,174.51027895826692</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>-35.68122910280671,174.51002782895267</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>-35.68196334683291,174.51006846549402</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-35.6826657734114,174.51033418586627</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>-35.683389872701795,174.51045627724187</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>-35.68409926064378,174.51067395767643</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>-35.684800215894015,174.51090034998273</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>-35.68544906174585,174.5112094328923</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>-35.68604631240835,174.5116935753464</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U283"/>
+  <dimension ref="A1:U285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19979,6 +19979,144 @@
       <c r="U283" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="C284" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="D284" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="E284" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="F284" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="G284" t="n">
+        <v>377.95</v>
+      </c>
+      <c r="H284" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="I284" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="J284" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="K284" t="n">
+        <v>392.55</v>
+      </c>
+      <c r="L284" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="M284" t="n">
+        <v>362.23</v>
+      </c>
+      <c r="N284" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="O284" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="P284" t="n">
+        <v>359.05</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="R284" t="n">
+        <v>373.36</v>
+      </c>
+      <c r="S284" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="T284" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="C285" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="D285" t="n">
+        <v>378.27</v>
+      </c>
+      <c r="E285" t="n">
+        <v>375.95</v>
+      </c>
+      <c r="F285" t="n">
+        <v>375.63</v>
+      </c>
+      <c r="G285" t="n">
+        <v>376.36</v>
+      </c>
+      <c r="H285" t="n">
+        <v>376.07</v>
+      </c>
+      <c r="I285" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="J285" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="K285" t="n">
+        <v>390.8</v>
+      </c>
+      <c r="L285" t="n">
+        <v>381.28</v>
+      </c>
+      <c r="M285" t="n">
+        <v>360.77</v>
+      </c>
+      <c r="N285" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="O285" t="n">
+        <v>364</v>
+      </c>
+      <c r="P285" t="n">
+        <v>357.65</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>364.26</v>
+      </c>
+      <c r="R285" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="S285" t="n">
+        <v>374.49</v>
+      </c>
+      <c r="T285" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19993,7 +20131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22906,6 +23044,26 @@
       </c>
       <c r="B291" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -23074,28 +23232,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01177481601886301</v>
+        <v>-0.01848056003647728</v>
       </c>
       <c r="J2" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K2" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001698551755150435</v>
+        <v>0.0004236884046860956</v>
       </c>
       <c r="M2" t="n">
-        <v>4.910897496080266</v>
+        <v>4.908101127361348</v>
       </c>
       <c r="N2" t="n">
-        <v>39.56924108547089</v>
+        <v>39.42562229411362</v>
       </c>
       <c r="O2" t="n">
-        <v>6.290408658065936</v>
+        <v>6.27898258431361</v>
       </c>
       <c r="P2" t="n">
-        <v>381.8477668481293</v>
+        <v>381.9248660230398</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23152,28 +23310,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01004070481035073</v>
+        <v>-0.02217085362550429</v>
       </c>
       <c r="J3" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K3" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001539261284816407</v>
+        <v>0.000751763646897663</v>
       </c>
       <c r="M3" t="n">
-        <v>4.372691261250619</v>
+        <v>4.390201706793939</v>
       </c>
       <c r="N3" t="n">
-        <v>31.75054735916888</v>
+        <v>31.96949847436787</v>
       </c>
       <c r="O3" t="n">
-        <v>5.63476240485514</v>
+        <v>5.654157627301158</v>
       </c>
       <c r="P3" t="n">
-        <v>384.1170407285041</v>
+        <v>384.2565082147644</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23230,28 +23388,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004280133672658685</v>
+        <v>-0.004701787925338572</v>
       </c>
       <c r="J4" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K4" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L4" t="n">
-        <v>3.505859311991877e-05</v>
+        <v>4.257952720621017e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.711784071726039</v>
+        <v>3.730825009817082</v>
       </c>
       <c r="N4" t="n">
-        <v>25.33418711231472</v>
+        <v>25.403038681285</v>
       </c>
       <c r="O4" t="n">
-        <v>5.033307770474077</v>
+        <v>5.040142724297101</v>
       </c>
       <c r="P4" t="n">
-        <v>385.0021337620487</v>
+        <v>385.1054113453774</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23308,28 +23466,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05780543178890189</v>
+        <v>0.04879696122510294</v>
       </c>
       <c r="J5" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K5" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005298916990456926</v>
+        <v>0.003812594358684307</v>
       </c>
       <c r="M5" t="n">
-        <v>4.096062229993032</v>
+        <v>4.114555748025694</v>
       </c>
       <c r="N5" t="n">
-        <v>30.41198673893595</v>
+        <v>30.44282318956543</v>
       </c>
       <c r="O5" t="n">
-        <v>5.514706405506638</v>
+        <v>5.517501535075947</v>
       </c>
       <c r="P5" t="n">
-        <v>380.9205717066847</v>
+        <v>381.0241493497322</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23386,28 +23544,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01224127413067524</v>
+        <v>-0.01252068092391933</v>
       </c>
       <c r="J6" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K6" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000219961879594055</v>
+        <v>0.0002337419841519361</v>
       </c>
       <c r="M6" t="n">
-        <v>4.376992304631526</v>
+        <v>4.357983744420839</v>
       </c>
       <c r="N6" t="n">
-        <v>33.02267915955773</v>
+        <v>32.80927014355916</v>
       </c>
       <c r="O6" t="n">
-        <v>5.746536274971014</v>
+        <v>5.727937686773413</v>
       </c>
       <c r="P6" t="n">
-        <v>377.7755250799579</v>
+        <v>377.7787613769585</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23464,28 +23622,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04479860310041603</v>
+        <v>0.0491927691861048</v>
       </c>
       <c r="J7" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K7" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001948609636412635</v>
+        <v>0.002384013777762983</v>
       </c>
       <c r="M7" t="n">
-        <v>4.991165631876927</v>
+        <v>4.977543608563808</v>
       </c>
       <c r="N7" t="n">
-        <v>49.83781814112839</v>
+        <v>49.54913812002351</v>
       </c>
       <c r="O7" t="n">
-        <v>7.059590508034329</v>
+        <v>7.03911486765371</v>
       </c>
       <c r="P7" t="n">
-        <v>373.0607389931098</v>
+        <v>373.0102314922681</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23542,28 +23700,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07336289435474355</v>
+        <v>-0.06488339162444712</v>
       </c>
       <c r="J8" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K8" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004332980249632579</v>
+        <v>0.00343430185966942</v>
       </c>
       <c r="M8" t="n">
-        <v>6.062376947926522</v>
+        <v>6.052192865565797</v>
       </c>
       <c r="N8" t="n">
-        <v>59.96286087043393</v>
+        <v>59.7741598624326</v>
       </c>
       <c r="O8" t="n">
-        <v>7.743569000818288</v>
+        <v>7.731375030512528</v>
       </c>
       <c r="P8" t="n">
-        <v>374.0424714140453</v>
+        <v>373.9450072245597</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23620,28 +23778,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1373845172135928</v>
+        <v>-0.1269979075375233</v>
       </c>
       <c r="J9" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K9" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01998364949444076</v>
+        <v>0.01727294898666076</v>
       </c>
       <c r="M9" t="n">
-        <v>5.362318704056776</v>
+        <v>5.375495644921583</v>
       </c>
       <c r="N9" t="n">
-        <v>44.87827136002507</v>
+        <v>44.89918681198272</v>
       </c>
       <c r="O9" t="n">
-        <v>6.699124671180935</v>
+        <v>6.700685547910954</v>
       </c>
       <c r="P9" t="n">
-        <v>375.3739234202064</v>
+        <v>375.2545305326391</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23698,28 +23856,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1063018832357741</v>
+        <v>-0.09566107083516814</v>
       </c>
       <c r="J10" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K10" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01315012436146679</v>
+        <v>0.01075760173015528</v>
       </c>
       <c r="M10" t="n">
-        <v>5.17340558067267</v>
+        <v>5.181514722251668</v>
       </c>
       <c r="N10" t="n">
-        <v>41.11546122334424</v>
+        <v>41.17528939338931</v>
       </c>
       <c r="O10" t="n">
-        <v>6.412133905599932</v>
+        <v>6.416797440576515</v>
       </c>
       <c r="P10" t="n">
-        <v>381.963741770885</v>
+        <v>381.8414235399533</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23776,28 +23934,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04678323688196376</v>
+        <v>-0.03072173789185846</v>
       </c>
       <c r="J11" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K11" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00112975477662236</v>
+        <v>0.0004913714532689406</v>
       </c>
       <c r="M11" t="n">
-        <v>7.8360599294974</v>
+        <v>7.865603092227079</v>
       </c>
       <c r="N11" t="n">
-        <v>93.82259539791693</v>
+        <v>93.93925439212899</v>
       </c>
       <c r="O11" t="n">
-        <v>9.686206450304315</v>
+        <v>9.692226493026718</v>
       </c>
       <c r="P11" t="n">
-        <v>382.3278911594139</v>
+        <v>382.1432470185663</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -23858,28 +24016,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06793098147186746</v>
+        <v>0.08010958829902265</v>
       </c>
       <c r="J12" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K12" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005655015153556375</v>
+        <v>0.007885282548825701</v>
       </c>
       <c r="M12" t="n">
-        <v>4.968060409146224</v>
+        <v>4.990123151893854</v>
       </c>
       <c r="N12" t="n">
-        <v>39.6737106798854</v>
+        <v>39.84137337435837</v>
       </c>
       <c r="O12" t="n">
-        <v>6.298707064143038</v>
+        <v>6.312002326865728</v>
       </c>
       <c r="P12" t="n">
-        <v>372.3033188063537</v>
+        <v>372.1637017781156</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -23940,28 +24098,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1279129893098621</v>
+        <v>-0.1233565129913934</v>
       </c>
       <c r="J13" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K13" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02911229935997484</v>
+        <v>0.02749434185873501</v>
       </c>
       <c r="M13" t="n">
-        <v>3.938546703177838</v>
+        <v>3.931222754949701</v>
       </c>
       <c r="N13" t="n">
-        <v>26.43547085604415</v>
+        <v>26.31330071378081</v>
       </c>
       <c r="O13" t="n">
-        <v>5.141543625803846</v>
+        <v>5.129649180380741</v>
       </c>
       <c r="P13" t="n">
-        <v>361.9220068758826</v>
+        <v>361.869447096278</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24018,28 +24176,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1836492213698742</v>
+        <v>-0.1891865063868835</v>
       </c>
       <c r="J14" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K14" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0396434054109146</v>
+        <v>0.04253029154548627</v>
       </c>
       <c r="M14" t="n">
-        <v>5.014792086861561</v>
+        <v>5.008213042071868</v>
       </c>
       <c r="N14" t="n">
-        <v>39.61336819267564</v>
+        <v>39.42629091387737</v>
       </c>
       <c r="O14" t="n">
-        <v>6.293915172027316</v>
+        <v>6.279035826771286</v>
       </c>
       <c r="P14" t="n">
-        <v>364.3071304659313</v>
+        <v>364.3707897625141</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24096,28 +24254,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1157267750628597</v>
+        <v>-0.1079543037592699</v>
       </c>
       <c r="J15" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K15" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02000718703143456</v>
+        <v>0.01763655834251199</v>
       </c>
       <c r="M15" t="n">
-        <v>4.358706463530633</v>
+        <v>4.355080642481712</v>
       </c>
       <c r="N15" t="n">
-        <v>31.80581870371724</v>
+        <v>31.76268432290969</v>
       </c>
       <c r="O15" t="n">
-        <v>5.639664768735571</v>
+        <v>5.635839274048692</v>
       </c>
       <c r="P15" t="n">
-        <v>362.0856819737992</v>
+        <v>361.9963247356407</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24174,28 +24332,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07780106395569293</v>
+        <v>-0.07789937068687525</v>
       </c>
       <c r="J16" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K16" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01091127933139824</v>
+        <v>0.01111406885965016</v>
       </c>
       <c r="M16" t="n">
-        <v>4.009183936406478</v>
+        <v>3.985969403848872</v>
       </c>
       <c r="N16" t="n">
-        <v>26.60312568850077</v>
+        <v>26.41921672690614</v>
       </c>
       <c r="O16" t="n">
-        <v>5.157821796892636</v>
+        <v>5.139962716489891</v>
       </c>
       <c r="P16" t="n">
-        <v>360.4864236280476</v>
+        <v>360.4875640329082</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24252,28 +24410,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.05944048028311513</v>
+        <v>-0.05458753776119116</v>
       </c>
       <c r="J17" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K17" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00778777850080814</v>
+        <v>0.006660049788164368</v>
       </c>
       <c r="M17" t="n">
-        <v>3.369863422103546</v>
+        <v>3.36588239838744</v>
       </c>
       <c r="N17" t="n">
-        <v>21.82516922255089</v>
+        <v>21.74634938636822</v>
       </c>
       <c r="O17" t="n">
-        <v>4.671741562046309</v>
+        <v>4.663298123256568</v>
       </c>
       <c r="P17" t="n">
-        <v>363.4290953870899</v>
+        <v>363.3733132503734</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24330,28 +24488,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03972564440908979</v>
+        <v>0.04744431125997814</v>
       </c>
       <c r="J18" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K18" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001983416609215083</v>
+        <v>0.00285885244514672</v>
       </c>
       <c r="M18" t="n">
-        <v>4.353190744368974</v>
+        <v>4.352683385182186</v>
       </c>
       <c r="N18" t="n">
-        <v>38.50062080513025</v>
+        <v>38.41599750136454</v>
       </c>
       <c r="O18" t="n">
-        <v>6.204886848696779</v>
+        <v>6.198064012364227</v>
       </c>
       <c r="P18" t="n">
-        <v>366.1352149437311</v>
+        <v>366.0464901621623</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24408,28 +24566,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0004175969203642084</v>
+        <v>0.008080721441813609</v>
       </c>
       <c r="J19" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K19" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L19" t="n">
-        <v>2.15462700570157e-07</v>
+        <v>8.150391747130392e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>4.623949373754232</v>
+        <v>4.627520418627204</v>
       </c>
       <c r="N19" t="n">
-        <v>39.24139155978418</v>
+        <v>39.1981268979367</v>
       </c>
       <c r="O19" t="n">
-        <v>6.264294977073172</v>
+        <v>6.260840750085942</v>
       </c>
       <c r="P19" t="n">
-        <v>370.4341921039756</v>
+        <v>370.3365106472356</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24486,28 +24644,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.08598169473415912</v>
+        <v>-0.07656633527284237</v>
       </c>
       <c r="J20" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K20" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01455443633949149</v>
+        <v>0.01163345996782694</v>
       </c>
       <c r="M20" t="n">
-        <v>3.710161291747044</v>
+        <v>3.723637638485434</v>
       </c>
       <c r="N20" t="n">
-        <v>24.26896573465774</v>
+        <v>24.37046301254766</v>
       </c>
       <c r="O20" t="n">
-        <v>4.926354203126054</v>
+        <v>4.936644914569778</v>
       </c>
       <c r="P20" t="n">
-        <v>378.8820286471527</v>
+        <v>378.7737961201868</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24545,7 +24703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U283"/>
+  <dimension ref="A1:U285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54801,6 +54959,220 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>-35.673506274054255,174.50830987974032</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>-35.67423428424591,174.5083741585206</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>-35.67495250066531,174.50848816424573</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-35.67567147320265,174.50859567319532</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-35.67638860779138,174.50875981973695</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-35.67711004739568,174.50889507753902</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>-35.67782762702724,174.50905529785794</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-35.678542721097315,174.50921227013933</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-35.67919577826876,174.50945501074173</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>-35.67973828507691,174.51001335261793</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-35.6804687434063,174.5102556237256</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-35.6812293325242,174.5100240830183</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-35.68196239964901,174.5100752165541</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-35.68266602269729,174.51033266952186</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>-35.683390766567605,174.51045052476707</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>-35.68409994882646,174.5106690577336</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>-35.68480192346339,174.51089187590193</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>-35.685454738176894,174.51119390480875</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>-35.68604875163031,174.51168841194362</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>-35.67350674269427,174.50830371987297</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>-35.674235288480425,174.50836095868584</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>-35.67495467134467,174.50846789993028</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-35.67567322382414,174.50858315072955</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-35.67639366697781,174.50872411714465</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-35.677112509540784,174.50887777239822</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-35.67783268837249,174.509020268092</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-35.67854766632383,174.50918170954293</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-35.67920481098312,174.50943043111542</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>-35.6797460572154,174.50999652750795</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-35.68047154345491,174.51023760728748</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>-35.68123031895678,174.510007997535</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>-35.681961956611254,174.51007837430794</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-35.6826664678506,174.51032996176394</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>-35.68339312772126,174.51043532954992</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>-35.68410234981784,174.51065196237664</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>-35.68480657064292,174.51086881352816</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>-35.68546609103311,174.51116284863488</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>-35.686057785783866,174.5116692882268</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U285"/>
+  <dimension ref="A1:U286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20115,6 +20115,75 @@
         <v>381.8</v>
       </c>
       <c r="U285" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="C286" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="D286" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="E286" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="F286" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="G286" t="n">
+        <v>374.84</v>
+      </c>
+      <c r="H286" t="n">
+        <v>375.17</v>
+      </c>
+      <c r="I286" t="n">
+        <v>376</v>
+      </c>
+      <c r="J286" t="n">
+        <v>384.69</v>
+      </c>
+      <c r="K286" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="L286" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="M286" t="n">
+        <v>360.69</v>
+      </c>
+      <c r="N286" t="n">
+        <v>357.76</v>
+      </c>
+      <c r="O286" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="P286" t="n">
+        <v>359.16</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>367</v>
+      </c>
+      <c r="R286" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="S286" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="T286" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="U286" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20131,7 +20200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23064,6 +23133,16 @@
       </c>
       <c r="B293" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -23232,28 +23311,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01848056003647728</v>
+        <v>-0.02192510142733989</v>
       </c>
       <c r="J2" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K2" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004236884046860956</v>
+        <v>0.0005999931902018751</v>
       </c>
       <c r="M2" t="n">
-        <v>4.908101127361348</v>
+        <v>4.906996477867485</v>
       </c>
       <c r="N2" t="n">
-        <v>39.42562229411362</v>
+        <v>39.35903801274872</v>
       </c>
       <c r="O2" t="n">
-        <v>6.27898258431361</v>
+        <v>6.27367818849108</v>
       </c>
       <c r="P2" t="n">
-        <v>381.9248660230398</v>
+        <v>381.9646319947545</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23310,28 +23389,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02217085362550429</v>
+        <v>-0.02745127740181286</v>
       </c>
       <c r="J3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000751763646897663</v>
+        <v>0.001155285690614072</v>
       </c>
       <c r="M3" t="n">
-        <v>4.390201706793939</v>
+        <v>4.396873570041039</v>
       </c>
       <c r="N3" t="n">
-        <v>31.96949847436787</v>
+        <v>32.02594286924928</v>
       </c>
       <c r="O3" t="n">
-        <v>5.654157627301158</v>
+        <v>5.659146832275098</v>
       </c>
       <c r="P3" t="n">
-        <v>384.2565082147644</v>
+        <v>384.3174687777837</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23388,28 +23467,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.004701787925338572</v>
+        <v>-0.008907692486513271</v>
       </c>
       <c r="J4" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K4" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L4" t="n">
-        <v>4.257952720621017e-05</v>
+        <v>0.0001534056771872461</v>
       </c>
       <c r="M4" t="n">
-        <v>3.730825009817082</v>
+        <v>3.738616743517631</v>
       </c>
       <c r="N4" t="n">
-        <v>25.403038681285</v>
+        <v>25.42088097581166</v>
       </c>
       <c r="O4" t="n">
-        <v>5.040142724297101</v>
+        <v>5.041912432382346</v>
       </c>
       <c r="P4" t="n">
-        <v>385.1054113453774</v>
+        <v>385.1539669766896</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23466,28 +23545,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04879696122510294</v>
+        <v>0.04280243211382712</v>
       </c>
       <c r="J5" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K5" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003812594358684307</v>
+        <v>0.002938790360045296</v>
       </c>
       <c r="M5" t="n">
-        <v>4.114555748025694</v>
+        <v>4.131211645209771</v>
       </c>
       <c r="N5" t="n">
-        <v>30.44282318956543</v>
+        <v>30.55331476662939</v>
       </c>
       <c r="O5" t="n">
-        <v>5.517501535075947</v>
+        <v>5.52750529322491</v>
       </c>
       <c r="P5" t="n">
-        <v>381.0241493497322</v>
+        <v>381.093353997908</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23544,28 +23623,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01252068092391933</v>
+        <v>-0.01497258538777293</v>
       </c>
       <c r="J6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002337419841519361</v>
+        <v>0.0003365603238782988</v>
       </c>
       <c r="M6" t="n">
-        <v>4.357983744420839</v>
+        <v>4.356324483139518</v>
       </c>
       <c r="N6" t="n">
-        <v>32.80927014355916</v>
+        <v>32.73050569332918</v>
       </c>
       <c r="O6" t="n">
-        <v>5.727937686773413</v>
+        <v>5.721058092112785</v>
       </c>
       <c r="P6" t="n">
-        <v>377.7787613769585</v>
+        <v>377.8070677180625</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23622,28 +23701,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0491927691861048</v>
+        <v>0.04957837438529531</v>
       </c>
       <c r="J7" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K7" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002384013777762983</v>
+        <v>0.002441034256017605</v>
       </c>
       <c r="M7" t="n">
-        <v>4.977543608563808</v>
+        <v>4.961952065936245</v>
       </c>
       <c r="N7" t="n">
-        <v>49.54913812002351</v>
+        <v>49.37618068682448</v>
       </c>
       <c r="O7" t="n">
-        <v>7.03911486765371</v>
+        <v>7.026818674679494</v>
       </c>
       <c r="P7" t="n">
-        <v>373.0102314922681</v>
+        <v>373.0057798211444</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23700,28 +23779,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06488339162444712</v>
+        <v>-0.06263946026495774</v>
       </c>
       <c r="J8" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K8" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00343430185966942</v>
+        <v>0.003225908624788443</v>
       </c>
       <c r="M8" t="n">
-        <v>6.052192865565797</v>
+        <v>6.039520574001545</v>
       </c>
       <c r="N8" t="n">
-        <v>59.7741598624326</v>
+        <v>59.59487585647975</v>
       </c>
       <c r="O8" t="n">
-        <v>7.731375030512528</v>
+        <v>7.719771748988421</v>
       </c>
       <c r="P8" t="n">
-        <v>373.9450072245597</v>
+        <v>373.9191018569518</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23778,28 +23857,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1269979075375233</v>
+        <v>-0.123857059969811</v>
       </c>
       <c r="J9" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K9" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01727294898666076</v>
+        <v>0.01655275121211597</v>
       </c>
       <c r="M9" t="n">
-        <v>5.375495644921583</v>
+        <v>5.371818502854847</v>
       </c>
       <c r="N9" t="n">
-        <v>44.89918681198272</v>
+        <v>44.80130265138719</v>
       </c>
       <c r="O9" t="n">
-        <v>6.700685547910954</v>
+        <v>6.693377521953113</v>
       </c>
       <c r="P9" t="n">
-        <v>375.2545305326391</v>
+        <v>375.2182705951423</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23856,28 +23935,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09566107083516814</v>
+        <v>-0.09155997914874861</v>
       </c>
       <c r="J10" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K10" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01075760173015528</v>
+        <v>0.009918933532872765</v>
       </c>
       <c r="M10" t="n">
-        <v>5.181514722251668</v>
+        <v>5.180597197802048</v>
       </c>
       <c r="N10" t="n">
-        <v>41.17528939338931</v>
+        <v>41.13252513195982</v>
       </c>
       <c r="O10" t="n">
-        <v>6.416797440576515</v>
+        <v>6.413464362726265</v>
       </c>
       <c r="P10" t="n">
-        <v>381.8414235399533</v>
+        <v>381.7940779349813</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23934,28 +24013,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03072173789185846</v>
+        <v>-0.02413211447212983</v>
       </c>
       <c r="J11" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K11" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004913714532689406</v>
+        <v>0.0003048522384411223</v>
       </c>
       <c r="M11" t="n">
-        <v>7.865603092227079</v>
+        <v>7.8723113493109</v>
       </c>
       <c r="N11" t="n">
-        <v>93.93925439212899</v>
+        <v>93.8722387642693</v>
       </c>
       <c r="O11" t="n">
-        <v>9.692226493026718</v>
+        <v>9.688768691854982</v>
       </c>
       <c r="P11" t="n">
-        <v>382.1432470185663</v>
+        <v>382.0671722240482</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24016,28 +24095,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08010958829902265</v>
+        <v>0.08526620025736041</v>
       </c>
       <c r="J12" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K12" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007885282548825701</v>
+        <v>0.008959714936429553</v>
       </c>
       <c r="M12" t="n">
-        <v>4.990123151893854</v>
+        <v>4.996834031362344</v>
       </c>
       <c r="N12" t="n">
-        <v>39.84137337435837</v>
+        <v>39.86121625267536</v>
       </c>
       <c r="O12" t="n">
-        <v>6.312002326865728</v>
+        <v>6.313573968258815</v>
       </c>
       <c r="P12" t="n">
-        <v>372.1637017781156</v>
+        <v>372.1043315034088</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24098,28 +24177,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1233565129913934</v>
+        <v>-0.1217388175206392</v>
       </c>
       <c r="J13" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K13" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02749434185873501</v>
+        <v>0.02699302371114298</v>
       </c>
       <c r="M13" t="n">
-        <v>3.931222754949701</v>
+        <v>3.924636394884895</v>
       </c>
       <c r="N13" t="n">
-        <v>26.31330071378081</v>
+        <v>26.23581749006183</v>
       </c>
       <c r="O13" t="n">
-        <v>5.129649180380741</v>
+        <v>5.122091124732343</v>
       </c>
       <c r="P13" t="n">
-        <v>361.869447096278</v>
+        <v>361.8507046505519</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24176,28 +24255,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1891865063868835</v>
+        <v>-0.1903582993326532</v>
       </c>
       <c r="J14" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K14" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04253029154548627</v>
+        <v>0.04336190442803889</v>
       </c>
       <c r="M14" t="n">
-        <v>5.008213042071868</v>
+        <v>4.996694584446541</v>
       </c>
       <c r="N14" t="n">
-        <v>39.42629091387737</v>
+        <v>39.29625668746579</v>
       </c>
       <c r="O14" t="n">
-        <v>6.279035826771286</v>
+        <v>6.268672641593736</v>
       </c>
       <c r="P14" t="n">
-        <v>364.3707897625141</v>
+        <v>364.3843176838973</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24254,28 +24333,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1079543037592699</v>
+        <v>-0.1044189440908126</v>
       </c>
       <c r="J15" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K15" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01763655834251199</v>
+        <v>0.01661212203598295</v>
       </c>
       <c r="M15" t="n">
-        <v>4.355080642481712</v>
+        <v>4.351938089946104</v>
       </c>
       <c r="N15" t="n">
-        <v>31.76268432290969</v>
+        <v>31.72682098695214</v>
       </c>
       <c r="O15" t="n">
-        <v>5.635839274048692</v>
+        <v>5.632656654452865</v>
       </c>
       <c r="P15" t="n">
-        <v>361.9963247356407</v>
+        <v>361.9555103000963</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24332,28 +24411,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07789937068687525</v>
+        <v>-0.07732122402550624</v>
       </c>
       <c r="J16" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K16" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01111406885965016</v>
+        <v>0.01103870683683728</v>
       </c>
       <c r="M16" t="n">
-        <v>3.985969403848872</v>
+        <v>3.973928291894909</v>
       </c>
       <c r="N16" t="n">
-        <v>26.41921672690614</v>
+        <v>26.32853907593495</v>
       </c>
       <c r="O16" t="n">
-        <v>5.139962716489891</v>
+        <v>5.131134287458763</v>
       </c>
       <c r="P16" t="n">
-        <v>360.4875640329082</v>
+        <v>360.4808895409587</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24410,28 +24489,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.05458753776119116</v>
+        <v>-0.05073039943495677</v>
       </c>
       <c r="J17" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K17" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L17" t="n">
-        <v>0.006660049788164368</v>
+        <v>0.00578000305843529</v>
       </c>
       <c r="M17" t="n">
-        <v>3.36588239838744</v>
+        <v>3.369926822995938</v>
       </c>
       <c r="N17" t="n">
-        <v>21.74634938636822</v>
+        <v>21.76001625595321</v>
       </c>
       <c r="O17" t="n">
-        <v>4.663298123256568</v>
+        <v>4.664763258296525</v>
       </c>
       <c r="P17" t="n">
-        <v>363.3733132503734</v>
+        <v>363.3287839978037</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24488,28 +24567,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04744431125997814</v>
+        <v>0.05086175352687594</v>
       </c>
       <c r="J18" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K18" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00285885244514672</v>
+        <v>0.003304663204321545</v>
       </c>
       <c r="M18" t="n">
-        <v>4.352683385182186</v>
+        <v>4.350729128130989</v>
       </c>
       <c r="N18" t="n">
-        <v>38.41599750136454</v>
+        <v>38.35183123195914</v>
       </c>
       <c r="O18" t="n">
-        <v>6.198064012364227</v>
+        <v>6.192885533574728</v>
       </c>
       <c r="P18" t="n">
-        <v>366.0464901621623</v>
+        <v>366.0070370399318</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24566,28 +24645,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008080721441813609</v>
+        <v>0.01118668472266759</v>
       </c>
       <c r="J19" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K19" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L19" t="n">
-        <v>8.150391747130392e-05</v>
+        <v>0.0001572228933878206</v>
       </c>
       <c r="M19" t="n">
-        <v>4.627520418627204</v>
+        <v>4.624484641884106</v>
       </c>
       <c r="N19" t="n">
-        <v>39.1981268979367</v>
+        <v>39.11892864034789</v>
       </c>
       <c r="O19" t="n">
-        <v>6.260840750085942</v>
+        <v>6.254512662098294</v>
       </c>
       <c r="P19" t="n">
-        <v>370.3365106472356</v>
+        <v>370.3006534360838</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24644,28 +24723,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07656633527284237</v>
+        <v>-0.07293878462630674</v>
       </c>
       <c r="J20" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K20" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01163345996782694</v>
+        <v>0.0106191733409341</v>
       </c>
       <c r="M20" t="n">
-        <v>3.723637638485434</v>
+        <v>3.725951436707553</v>
       </c>
       <c r="N20" t="n">
-        <v>24.37046301254766</v>
+        <v>24.36453071076594</v>
       </c>
       <c r="O20" t="n">
-        <v>4.936644914569778</v>
+        <v>4.936044034524605</v>
       </c>
       <c r="P20" t="n">
-        <v>378.7737961201868</v>
+        <v>378.7319173734873</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24703,7 +24782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U285"/>
+  <dimension ref="A1:U286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55173,6 +55252,113 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>-35.67350670085142,174.50830426986113</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>-35.674234083398844,174.50837679848755</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>-35.674953310270446,174.5084806062039</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-35.67567555290987,174.50856649040458</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-35.676395857232094,174.50870866053307</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-35.67711486328727,174.50886122911788</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-35.67783410303241,174.5090104771628</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-35.67854968299202,174.5091692468872</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-35.679205699446555,174.50942801344698</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-35.67974952136782,174.509989028315</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-35.68047186394223,174.510235545165</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-35.681230373007814,174.51000711613867</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-35.68195911505678,174.5100986274869</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-35.6826668773916,174.51032747062663</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-35.6833905810483,174.51045171867693</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>-35.68409815955106,174.51068179758482</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>-35.68480523052647,174.51087546407345</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>-35.68546550127454,174.51116446194283</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>-35.68605909573587,174.51166651528752</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
